--- a/02_加值成品/八下/八下6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-2 常見的力　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下6-2 常見的力　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>地球吸引物體的力是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>走路/煞車</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>向下</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>重力的方向是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>形變與力成正比刻度線性</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>有害:耗能;有益:走路煞車</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>向下(指向地心)</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不能測重量,可用其他法</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>恆向下</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>阻礙物體相對運動的力是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>摩擦力</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>阻礙</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>摩擦力方向與運動？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>相反</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>摩擦力</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>正向力</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>阻礙</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>彈簧形變產生的力是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>靜摩擦</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>彈力</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>正向力</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>恢復</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>形變量與外力成正比是什麼定律？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>摩擦力小</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>摩擦力</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>虎克定律</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>彈簧</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>接觸面垂直的支撐力是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>正向力</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>走路/煞車</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>摩擦力小</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>垂直</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>彈簧秤利用什麼原理？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>虎克定律</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>動摩擦</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>正向力</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>測力</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>物體因地球吸引而受的力是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>重力</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>走路/煞車</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>向下</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>阻礙物體運動的接觸力是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>摩擦力</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>靜摩擦</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>摩擦</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-2 常見的力　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下6-2 常見的力　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>物體質量越大重力？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>靜摩擦</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>動摩擦</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>正向力</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>彈簧掛2N伸長1cm,掛4N伸長？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>向下(指向地心)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>大小相等(平衡)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>2cm</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>推箱子未動時摩擦力屬？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>靜摩擦</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>未動</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>物體滑動時摩擦屬？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>動摩擦</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>運動</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>水平桌面靜止書本,正向力與重力？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>形變與力成正比刻度線性</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>有害:耗能;有益:走路煞車</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>大小相等方向相反</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>正向力小於重力(僅垂直分量)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>摩擦力有用的例子？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>摩擦力小</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>走路/煞車</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>有益</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>虎克定律範圍是彈簧在？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>彈性限度內</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>正向力</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>範圍</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>冰面走路易滑因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>摩擦力小</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>彈力</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>低摩擦</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>質量越大所受重力？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>冰面比柏油路摩擦力？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>彈性限度內</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>重力</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>低摩擦</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-2 常見的力　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下6-2 常見的力　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>彈簧原長10cm掛3N變13cm,掛6N長？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>彈性限度內</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>16cm</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>虎克定律</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>形變正比</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>斜面上物體正向力與重力關係？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>正向力小於重力(僅垂直分量)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>向下(指向地心)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>大小相等方向相反</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>形變與力成正比刻度線性</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>分量</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>為何摩擦力既有害又有益?各舉例</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>形變與力成正比刻度線性</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不能測重量,可用其他法</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>有害:耗能;有益:走路煞車</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>大小相等(平衡)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>雙面</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>用虎克定律解釋彈簧秤刻度均勻？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>有害:耗能;有益:走路煞車</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>向下(指向地心)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>正向力小於重力(僅垂直分量)</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>形變與力成正比刻度線性</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>靜摩擦與動摩擦一般何者較大？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>最大靜摩擦較大</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>大小相等方向相反</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>有害:耗能;有益:走路煞車</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>不能測重量,可用其他法</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>比較</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>太空無重力彈簧秤能測質量嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>有害:耗能;有益:走路煞車</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>正向力小於重力(僅垂直分量)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>不能測重量,可用其他法</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>大小相等方向相反</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>情境</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>物體等速滑行摩擦力與拉力關係？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>大小相等(平衡)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>形變與力成正比刻度線性</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不能測重量,可用其他法</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>正向力小於重力(僅垂直分量)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>等速</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>增加接觸面粗糙度摩擦力如何？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>增大</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>彈力</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>靜摩擦</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>摩擦力</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>影響</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>彈簧掛4N伸2cm,掛6N伸幾cm？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>3cm</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>摩擦力小</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>摩擦力</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>大小相等(平衡)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>走路能前進與哪種力有關？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>摩擦力</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>靜摩擦</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>彈力</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>摩擦</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>向下</t>
+          <t>向下：地球會吸引地表附近的物體，這股力稱為重力，方向朝向地心</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>恆向下</t>
+          <t>恆向下：重力是地球對物體的吸引力，方向永遠指向地球中心，也就是我們感覺的「向下」</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>阻礙</t>
+          <t>阻礙：兩物體接觸面之間有相對運動或相對運動趨勢時，會產生阻礙這個運動的力，稱為摩擦力</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>阻礙</t>
+          <t>阻礙：摩擦力的方向永遠和物體運動(或運動趨勢)的方向相反，用來阻礙相對滑動</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>恢復</t>
+          <t>恢復：彈簧受外力拉伸或壓縮產生形變後，會產生一股想要恢復原狀的力，稱為彈力</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>彈簧</t>
+          <t>彈簧：虎克定律指出，在彈性限度內，彈簧的形變量(伸長或壓縮量)和所受外力大小成正比</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>垂直</t>
+          <t>垂直：物體放在接觸面上，接觸面會給物體一個垂直於接觸面、向外頂的支撐力，稱為正向力</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>測力</t>
+          <t>測力：彈簧秤利用虎克定律，彈簧伸長量與所受力成正比的特性，透過讀取伸長量來換算出力的大小</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>向下</t>
+          <t>向下：地球會吸引地表附近的物體，這股向下的吸引力稱為重力</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>摩擦</t>
+          <t>摩擦：兩物體表面接觸並有相對運動或相對運動趨勢時，會產生阻礙運動的摩擦力</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：物體所受的重力與其質量成正比，質量越大，受到的重力也越大</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：形變量與外力成正比，2牛頓對應1公分，力變成兩倍(4牛頓)，伸長量也變成兩倍，等於2公分</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>未動</t>
+          <t>未動：推力還不足以讓箱子開始滑動時，接觸面產生的摩擦力屬於靜摩擦力，此時摩擦力大小會隨推力增加而增加，直到達到最大值</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>運動</t>
+          <t>運動：物體已經開始相對滑動時，接觸面產生的摩擦力屬於動摩擦力</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：書本靜止在水平桌面上，代表受力平衡，桌面給書本向上的正向力必須和書本受到向下的重力大小相等、方向相反，兩者才會互相抵消</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>有益</t>
+          <t>有益：走路時腳底與地面的摩擦力讓人不會打滑，能順利前進；煞車時輪胎與地面的摩擦力讓車子能減速停下，這些都是摩擦力帶來好處的例子</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>範圍</t>
+          <t>範圍：虎克定律只在彈簧的彈性限度以內成立，形變量與外力成正比；一旦超過彈性限度，彈簧可能永久變形，不再符合虎克定律</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>低摩擦</t>
+          <t>低摩擦：冰面非常光滑，接觸面之間的摩擦力比一般地面小很多，所以在冰面上走路容易打滑</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：物體所受的重力與其質量成正比關係，質量越大，受到的重力也越大</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>低摩擦</t>
+          <t>低摩擦：冰面比柏油路光滑許多，接觸面之間的摩擦力比較小，這也是在冰面上容易打滑的原因</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>形變正比</t>
+          <t>形變正比：掛3N伸長了13−10=3公分，形變量與力成正比，掛6N(力變2倍)伸長量也變2倍，等於6公分，總長度=原長10+伸長6=16公分</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分量</t>
+          <t>分量：物體在斜面上，重力可以分解成平行斜面和垂直斜面兩個分量，斜面給物體的正向力只需要平衡垂直斜面的那個分量，所以正向力會小於物體所受的總重力</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>雙面</t>
+          <t>雙面：摩擦力會使機械運轉時產生多餘的熱能而浪費能量，這是有害的一面(例如機器零件磨損)；但走路靠摩擦力才不會打滑、煞車靠摩擦力才能減速停止，這些是摩擦力有益的一面，可見摩擦力有好有壞，要看情境判斷</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：因為彈簧的形變量和所受力成正比關係(虎克定律)，力每增加固定量，伸長量也固定增加同樣的比例，所以彈簧秤上的刻度可以均勻等距分布，呈線性關係</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>比較</t>
+          <t>比較：一般而言，物體要從靜止開始滑動所需克服的最大靜摩擦力，會比它已經滑動時所受到的動摩擦力來得大，這也是為什麼推動靜止物體一開始比較費力</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>情境</t>
+          <t>情境：彈簧秤是靠重力拉伸彈簧來測量重量的，在無重力(失重)的太空環境中沒有重力可以拉伸彈簧，所以彈簧秤無法正常測量；但質量本身與重力無關，可以改用測量慣性大小的其他方法來測定質量</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>等速</t>
+          <t>等速：物體做等速度運動代表合力為零(牛頓第一運動定律)，此時施加的拉力必須和阻礙運動的摩擦力大小相等、方向相反，兩者互相抵消才能維持等速</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>影響</t>
+          <t>影響：接觸面越粗糙，表面凹凸不平的程度越大，彼此卡住牽制的效果越明顯，摩擦力也會跟著增大</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：彈簧伸長量與所受的力成正比，4牛頓對應2公分，等於每牛頓伸長0.5公分，6牛頓則伸長6×0.5=3公分</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>摩擦</t>
+          <t>摩擦：走路時腳向後蹬地面，靠著鞋底與地面間的摩擦力提供反作用力，才能推動身體向前移動，如果沒有摩擦力(如在極滑的冰面上)就很難走路前進</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-2_三種難度測驗卷.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>虎克定律</t>
+          <t>彈性限度內</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>正向力</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>彈力</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>越大</t>
+          <t>靜摩擦</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>靜摩擦</t>
+          <t>走路/煞車</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>重力</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>向下(指向地心)</t>
+          <t>3cm</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>大小相等(平衡)</t>
+          <t>動摩擦</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>摩擦力</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>虎克定律</t>
+          <t>彈性限度內</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>彈力</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>彈力</t>
+          <t>正向力</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>走路/煞車</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>彈性限度內</t>
+          <t>重力</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>重力</t>
+          <t>摩擦力</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>彈性限度內</t>
+          <t>摩擦力</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>靜摩擦</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>虎克定律</t>
+          <t>正向力</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>摩擦力小</t>
+          <t>2cm</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>靜摩擦</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>摩擦力</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>大小相等(平衡)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>重力</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>彈力</t>
+          <t>正向力</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
